--- a/augmented_output.xlsx
+++ b/augmented_output.xlsx
@@ -139,13 +139,13 @@
     <t>All data available regarding sample material; processing parameters; and EBSD/XRD data should be parsed and reported here.</t>
   </si>
   <si>
-    <t>['https://data.htmdec.org/#item/68925d2c763d1fdc73dec4b0', 'https://data.htmdec.org/#item/68925d31763d1fdc73dec4b6', 'https://data.htmdec.org/#item/68925d37763d1fdc73dec4ce', 'https://data.htmdec.org/#item/68925d3b763d1fdc73dec4da', 'https://data.htmdec.org/#item/68925d40763d1fdc73dec4fb', 'https://data.htmdec.org/#item/68925d45763d1fdc73dec516', 'https://data.htmdec.org/#item/68925d4a763d1fdc73dec531', 'https://data.htmdec.org/#item/68925d4e763d1fdc73dec54c', 'https://data.htmdec.org/#item/68925d52763d1fdc73dec564', 'https://data.htmdec.org/#item/68925d56763d1fdc73dec582', 'https://data.htmdec.org/#item/68925d5a763d1fdc73dec594', 'https://data.htmdec.org/#item/68925d5f763d1fdc73dec5b2', 'https://data.htmdec.org/#item/68925d64763d1fdc73dec5d3', 'https://data.htmdec.org/#item/68925d68763d1fdc73dec5df', 'https://data.htmdec.org/#item/68925d6c763d1fdc73dec5f3', 'https://data.htmdec.org/#item/68925d71763d1fdc73dec618', 'https://data.htmdec.org/#item/68925d75763d1fdc73dec63c', 'https://data.htmdec.org/#item/68925d7a763d1fdc73dec663', 'https://data.htmdec.org/#item/68925d80763d1fdc73dec675', 'https://data.htmdec.org/#item/68925d84763d1fdc73dec68a', 'https://data.htmdec.org/#item/68925d88763d1fdc73dec69f', 'https://data.htmdec.org/#item/68925d8c763d1fdc73dec6b4', 'https://data.htmdec.org/#item/68925d90763d1fdc73dec6b7', 'https://data.htmdec.org/#item/68925d94763d1fdc73dec6cc', 'https://data.htmdec.org/#item/68925d97763d1fdc73dec6e1', 'https://data.htmdec.org/#item/68925d9b763d1fdc73dec6f0', 'https://data.htmdec.org/#item/68925d9f763d1fdc73dec6f9', 'https://data.htmdec.org/#item/68925da2763d1fdc73dec702', 'https://data.htmdec.org/#item/68925da7763d1fdc73dec70e', 'https://data.htmdec.org/#item/68925dab763d1fdc73dec717', 'https://data.htmdec.org/#item/68925daf763d1fdc73dec720', 'https://data.htmdec.org/#item/68925db3763d1fdc73dec723', 'https://data.htmdec.org/#item/68925db8763d1fdc73dec732', 'https://data.htmdec.org/#item/68925dbd763d1fdc73dec73b', 'https://data.htmdec.org/#item/68925dbd763d1fdc73dec73e', 'https://data.htmdec.org/#item/68925dc0763d1fdc73dec74a', 'https://data.htmdec.org/#item/68925dc3763d1fdc73dec750', 'https://data.htmdec.org/#item/68925dc4763d1fdc73dec75f', 'https://data.htmdec.org/#item/68925dc7763d1fdc73dec762', 'https://data.htmdec.org/#item/68925dc9763d1fdc73dec76e', 'https://data.htmdec.org/#item/68925dcb763d1fdc73dec77a', 'https://data.htmdec.org/#item/68925dce763d1fdc73dec783', 'https://data.htmdec.org/#item/68925dcf763d1fdc73dec786', 'https://data.htmdec.org/#item/68925dd3763d1fdc73dec795', 'https://data.htmdec.org/#item/68925dd3763d1fdc73dec798', 'https://data.htmdec.org/#item/68925dd6763d1fdc73dec7a7', 'https://data.htmdec.org/#item/68925dd8763d1fdc73dec7aa', 'https://data.htmdec.org/#item/68925dd9763d1fdc73dec7b6', 'https://data.htmdec.org/#item/68925ddd763d1fdc73dec7c9', 'https://data.htmdec.org/#item/68925ddd763d1fdc73dec7ca', 'https://data.htmdec.org/#item/68925de1763d1fdc73dec7ce', 'https://data.htmdec.org/#item/68925de3763d1fdc73dec7da', 'https://data.htmdec.org/#item/68925de5763d1fdc73dec7e0', 'https://data.htmdec.org/#item/68925de8763d1fdc73dec7e9', 'https://data.htmdec.org/#item/68925deb763d1fdc73dec7f8', 'https://data.htmdec.org/#item/68925ded763d1fdc73dec801', 'https://data.htmdec.org/#item/68925df0763d1fdc73dec80a', 'https://data.htmdec.org/#item/68925df2763d1fdc73dec813', 'https://data.htmdec.org/#item/68925df5763d1fdc73dec81c', 'https://data.htmdec.org/#item/68925df6763d1fdc73dec81f', 'https://data.htmdec.org/#item/68925dfa763d1fdc73dec828', 'https://data.htmdec.org/#item/68925dfa763d1fdc73dec834', 'https://data.htmdec.org/#item/68925dfe763d1fdc73dec83d', 'https://data.htmdec.org/#item/68925e02763d1fdc73dec849', 'https://data.htmdec.org/#item/6892693b763d1fdc73dec89a', 'https://data.htmdec.org/#item/68926942763d1fdc73dec8af', 'https://data.htmdec.org/#item/68926946763d1fdc73dec8bb', 'https://data.htmdec.org/#item/68926974763d1fdc73dec8e5', 'https://data.htmdec.org/#item/68926977763d1fdc73dec8ee', 'https://data.htmdec.org/#item/68a4806241a818bc1e9fd7e5', 'https://data.htmdec.org/#item/68a4806841a818bc1e9fd7fd', 'https://data.htmdec.org/#item/68a4806c41a818bc1e9fd815', 'https://data.htmdec.org/#item/68a4807141a818bc1e9fd830', 'https://data.htmdec.org/#item/68a4807641a818bc1e9fd84e', 'https://data.htmdec.org/#item/68a4807b41a818bc1e9fd866', 'https://data.htmdec.org/#item/68a4807f41a818bc1e9fd884', 'https://data.htmdec.org/#item/68a603b58ea78c936a438aad', 'https://data.htmdec.org/#item/68a603f08ea78c936a438ac6', 'https://data.htmdec.org/#item/68a603f58ea78c936a438ad3', 'https://data.htmdec.org/#item/68a6044a8ea78c936a438b1a', 'https://data.htmdec.org/#item/68a6044f8ea78c936a438b23', 'https://data.htmdec.org/#item/68a604548ea78c936a438b2f', 'https://data.htmdec.org/#item/68a604588ea78c936a438b38', 'https://data.htmdec.org/#item/68a6045e8ea78c936a438b41', 'https://data.htmdec.org/#item/68a604648ea78c936a438b56', 'https://data.htmdec.org/#item/68a6046d8ea78c936a438b5c', 'https://data.htmdec.org/#item/68a604718ea78c936a438b71', 'https://data.htmdec.org/#item/68a604a58ea78c936a438b92', 'https://data.htmdec.org/#item/68a604a98ea78c936a438b9b', 'https://data.htmdec.org/#item/68a604ae8ea78c936a438baa', 'https://data.htmdec.org/#item/68a604b28ea78c936a438bb3', 'https://data.htmdec.org/#item/68a604b78ea78c936a438bbc', 'https://data.htmdec.org/#item/691354e2e8c9c85bfb382a36', 'https://data.htmdec.org/#item/691354e6e8c9c85bfb382a3f', 'https://data.htmdec.org/#item/691354e99ca0e7d06ecd32d7', 'https://data.htmdec.org/#item/691354ed229b1dbc1a7371f7', 'https://data.htmdec.org/#item/691354f19ca0e7d06ecd32ef', 'https://data.htmdec.org/#item/691354f49ca0e7d06ecd3304', 'https://data.htmdec.org/#item/691354fde8c9c85bfb382a63', 'https://data.htmdec.org/#item/69135500229b1dbc1a737236', 'https://data.htmdec.org/#item/6913550378f878bb036510e7', 'https://data.htmdec.org/#item/69135507229b1dbc1a737257', 'https://data.htmdec.org/#item/6913550b229b1dbc1a737272', 'https://data.htmdec.org/#item/6913550f78f878bb036510ed', 'https://data.htmdec.org/#item/69135513e8c9c85bfb382a8a', 'https://data.htmdec.org/#item/69135516e8c9c85bfb382a9f', 'https://data.htmdec.org/#item/6913551a78f878bb03651111', 'https://data.htmdec.org/#item/6913551d78f878bb0365111a', 'https://data.htmdec.org/#item/69135520e8c9c85bfb382af9', 'https://data.htmdec.org/#item/6913552478f878bb03651147', 'https://data.htmdec.org/#item/69135528e8c9c85bfb382b23', 'https://data.htmdec.org/#item/6913552be8c9c85bfb382b3b', 'https://data.htmdec.org/#item/6913552e78f878bb03651174', 'https://data.htmdec.org/#item/69135531e8c9c85bfb382b60', 'https://data.htmdec.org/#item/69135536e8c9c85bfb382b89', 'https://data.htmdec.org/#item/69135539e8c9c85bfb382b95', 'https://data.htmdec.org/#item/6913553e78f878bb036511b6', 'https://data.htmdec.org/#item/69135542e8c9c85bfb382bb0', 'https://data.htmdec.org/#item/691355459ca0e7d06ecd3322', 'https://data.htmdec.org/#item/69135548e8c9c85bfb382bd4', 'https://data.htmdec.org/#item/6913554be8c9c85bfb382bf8', 'https://data.htmdec.org/#item/6913554fe8c9c85bfb382c22', 'https://data.htmdec.org/#item/69135552229b1dbc1a73730b', 'https://data.htmdec.org/#item/69135556e8c9c85bfb382c43', 'https://data.htmdec.org/#item/69135559e8c9c85bfb382c5e', 'https://data.htmdec.org/#item/6913555de8c9c85bfb382c82', 'https://data.htmdec.org/#item/69135560229b1dbc1a73734d', 'https://data.htmdec.org/#item/6913556478f878bb03651201', 'https://data.htmdec.org/#item/6913556878f878bb0365121c', 'https://data.htmdec.org/#item/6913556c78f878bb0365122b', 'https://data.htmdec.org/#item/691355709ca0e7d06ecd3334', 'https://data.htmdec.org/#item/6913557378f878bb03651243', 'https://data.htmdec.org/#item/6913557678f878bb03651252', 'https://data.htmdec.org/#item/6913557978f878bb03651261', 'https://data.htmdec.org/#item/6913557d9ca0e7d06ecd3376', 'https://data.htmdec.org/#item/691355809ca0e7d06ecd338b', 'https://data.htmdec.org/#item/69135584e8c9c85bfb382d1e', 'https://data.htmdec.org/#item/6913558778f878bb03651291', 'https://data.htmdec.org/#item/6913558ae8c9c85bfb382d42', 'https://data.htmdec.org/#item/6913558d78f878bb036512b5', 'https://data.htmdec.org/#item/6913559178f878bb036512ca', 'https://data.htmdec.org/#item/691355959ca0e7d06ecd33b2', 'https://data.htmdec.org/#item/691355999ca0e7d06ecd33bb', 'https://data.htmdec.org/#item/6913559ce8c9c85bfb382d78', 'https://data.htmdec.org/#item/691355a078f878bb03651300', 'https://data.htmdec.org/#item/691355a39ca0e7d06ecd33df', 'https://data.htmdec.org/#item/691355a7e8c9c85bfb382d9f', 'https://data.htmdec.org/#item/691355aa229b1dbc1a73738c', 'https://data.htmdec.org/#item/691355ad229b1dbc1a737398', 'https://data.htmdec.org/#item/691355b1229b1dbc1a7373aa', 'https://data.htmdec.org/#item/691355b4e8c9c85bfb382dcf', 'https://data.htmdec.org/#item/691355b79ca0e7d06ecd3400', 'https://data.htmdec.org/#item/691355bae8c9c85bfb382e17', 'https://data.htmdec.org/#item/691355bee8c9c85bfb382e3e', 'https://data.htmdec.org/#item/691355c2e8c9c85bfb382e7d', 'https://data.htmdec.org/#item/691355c7e8c9c85bfb382eb6', 'https://data.htmdec.org/#item/691355cb229b1dbc1a7373b6', 'https://data.htmdec.org/#item/691355ce229b1dbc1a7373cb', 'https://data.htmdec.org/#item/691355d29ca0e7d06ecd3409', 'https://data.htmdec.org/#item/691355d5229b1dbc1a73741f', 'https://data.htmdec.org/#item/691355d9229b1dbc1a73743d', 'https://data.htmdec.org/#item/691355dce8c9c85bfb382f19', 'https://data.htmdec.org/#item/691355e0229b1dbc1a737467', 'https://data.htmdec.org/#item/691355e3e8c9c85bfb382f3b', 'https://data.htmdec.org/#item/691355e7e8c9c85bfb382f61', 'https://data.htmdec.org/#item/691355eae8c9c85bfb382f7c', 'https://data.htmdec.org/#item/691355ede8c9c85bfb382f94', 'https://data.htmdec.org/#item/691355f1e8c9c85bfb382faf', 'https://data.htmdec.org/#item/691355f4229b1dbc1a7374ac', 'https://data.htmdec.org/#item/691355f7229b1dbc1a7374c1', 'https://data.htmdec.org/#item/691355fa9ca0e7d06ecd3457', 'https://data.htmdec.org/#item/691355fe9ca0e7d06ecd3472', 'https://data.htmdec.org/#item/69135601229b1dbc1a737500', 'https://data.htmdec.org/#item/691356059ca0e7d06ecd348d', 'https://data.htmdec.org/#item/691356089ca0e7d06ecd349c', 'https://data.htmdec.org/#item/6913560b229b1dbc1a737554', 'https://data.htmdec.org/#item/6913560fe8c9c85bfb382fdf', 'https://data.htmdec.org/#item/691356129ca0e7d06ecd34cf', 'https://data.htmdec.org/#item/69135615229b1dbc1a73757e', 'https://data.htmdec.org/#item/69135619229b1dbc1a7375a2', 'https://data.htmdec.org/#item/6913561c229b1dbc1a7375c6', 'https://data.htmdec.org/#item/69135620229b1dbc1a7375ea', 'https://data.htmdec.org/#item/69135623e8c9c85bfb382ff1', 'https://data.htmdec.org/#item/69135626229b1dbc1a737617', 'https://data.htmdec.org/#item/6913562ae8c9c85bfb383012', 'https://data.htmdec.org/#item/6913562d229b1dbc1a73763b', 'https://data.htmdec.org/#item/69135631e8c9c85bfb383021', 'https://data.htmdec.org/#item/69135635e8c9c85bfb38302a', 'https://data.htmdec.org/#item/6913563a229b1dbc1a737677', 'https://data.htmdec.org/#item/6913563e9ca0e7d06ecd350b', 'https://data.htmdec.org/#item/691356429ca0e7d06ecd3529', 'https://data.htmdec.org/#item/6913564578f878bb0365133f', 'https://data.htmdec.org/#item/6913564978f878bb0365135a', 'https://data.htmdec.org/#item/6913564c78f878bb03651378', 'https://data.htmdec.org/#item/6913564f78f878bb0365138d', 'https://data.htmdec.org/#item/6913565278f878bb036513ae', 'https://data.htmdec.org/#item/69135656e8c9c85bfb383063', 'https://data.htmdec.org/#item/6913565ae8c9c85bfb383075']</t>
-  </si>
-  <si>
-    <t>['https://data.htmdec.org/#item/68f7cdd35960472ae0ec92fa', 'https://data.htmdec.org/#item/68f7ce1b18f9fc1d4a340d3c', 'https://data.htmdec.org/#item/68f7ce1e5960472ae0ec930f', 'https://data.htmdec.org/#item/68f7ce645960472ae0ec931b', 'https://data.htmdec.org/#item/68f7ce6818f9fc1d4a340d5d', 'https://data.htmdec.org/#item/68f7ceb65960472ae0ec932d', 'https://data.htmdec.org/#item/68f7ceb95960472ae0ec9339', 'https://data.htmdec.org/#item/68f7cebb68c2cae708b4c4bc', 'https://data.htmdec.org/#item/68f7cf0818f9fc1d4a340d90', 'https://data.htmdec.org/#item/68f7cf0b18f9fc1d4a340d93', 'https://data.htmdec.org/#item/68f7cf56e440f024d10bfd5e', 'https://data.htmdec.org/#item/68f7cf59e440f024d10bfd67', 'https://data.htmdec.org/#item/68f7cfa218f9fc1d4a340db4', 'https://data.htmdec.org/#item/68f7cfa55960472ae0ec934b', 'https://data.htmdec.org/#item/68f7cfa818f9fc1d4a340dc0', 'https://data.htmdec.org/#item/68f7cff518f9fc1d4a340dcf', 'https://data.htmdec.org/#item/68f7cff718f9fc1d4a340dd2', 'https://data.htmdec.org/#item/68f7d042e440f024d10bfd73', 'https://data.htmdec.org/#item/68f7d046e440f024d10bfd82', 'https://data.htmdec.org/#item/68f7d04968c2cae708b4c4e3', 'https://data.htmdec.org/#item/68f7d09168c2cae708b4c4fb', 'https://data.htmdec.org/#item/68f7d0935960472ae0ec9360', 'https://data.htmdec.org/#item/68f7d0e268c2cae708b4c507', 'https://data.htmdec.org/#item/68f7d0e518f9fc1d4a340df3', 'https://data.htmdec.org/#item/68f7d12e5960472ae0ec937b']</t>
-  </si>
-  <si>
-    <t>[]</t>
+    <t>{'scan_point_0_xrd.csv': 'https://data.htmdec.org/#item/691354fde8c9c85bfb382a63', 'scan_point_10_xrd.csv': 'https://data.htmdec.org/#item/69135500229b1dbc1a737236', 'scan_point_11_xrd.csv': 'https://data.htmdec.org/#item/6913550378f878bb036510e7', 'scan_point_12_xrd.csv': 'https://data.htmdec.org/#item/69135507229b1dbc1a737257', 'scan_point_13_xrd.csv': 'https://data.htmdec.org/#item/6913550b229b1dbc1a737272', 'scan_point_14_xrd.csv': 'https://data.htmdec.org/#item/6913550f78f878bb036510ed', 'scan_point_15_xrd.csv': 'https://data.htmdec.org/#item/69135513e8c9c85bfb382a8a', 'scan_point_16_xrd.csv': 'https://data.htmdec.org/#item/69135516e8c9c85bfb382a9f', 'scan_point_17_xrd.csv': 'https://data.htmdec.org/#item/6913551a78f878bb03651111', 'scan_point_18_xrd.csv': 'https://data.htmdec.org/#item/6913551d78f878bb0365111a', 'scan_point_19_xrd.csv': 'https://data.htmdec.org/#item/69135520e8c9c85bfb382af9', 'scan_point_1_xrd.csv': 'https://data.htmdec.org/#item/6913552478f878bb03651147', 'scan_point_20_xrd.csv': 'https://data.htmdec.org/#item/69135528e8c9c85bfb382b23', 'scan_point_21_xrd.csv': 'https://data.htmdec.org/#item/6913552be8c9c85bfb382b3b', 'scan_point_22_xrd.csv': 'https://data.htmdec.org/#item/6913552e78f878bb03651174', 'scan_point_23_xrd.csv': 'https://data.htmdec.org/#item/69135531e8c9c85bfb382b60', 'scan_point_24_xrd.csv': 'https://data.htmdec.org/#item/69135536e8c9c85bfb382b89', 'scan_point_25_xrd.csv': 'https://data.htmdec.org/#item/69135539e8c9c85bfb382b95', 'scan_point_26_xrd.csv': 'https://data.htmdec.org/#item/6913553e78f878bb036511b6', 'scan_point_27_xrd.csv': 'https://data.htmdec.org/#item/69135542e8c9c85bfb382bb0', 'scan_point_28_xrd.csv': 'https://data.htmdec.org/#item/691355459ca0e7d06ecd3322', 'scan_point_29_xrd.csv': 'https://data.htmdec.org/#item/69135548e8c9c85bfb382bd4', 'scan_point_2_xrd.csv': 'https://data.htmdec.org/#item/6913554be8c9c85bfb382bf8', 'scan_point_30_xrd.csv': 'https://data.htmdec.org/#item/6913554fe8c9c85bfb382c22', 'scan_point_31_xrd.csv': 'https://data.htmdec.org/#item/69135552229b1dbc1a73730b', 'scan_point_32_xrd.csv': 'https://data.htmdec.org/#item/69135556e8c9c85bfb382c43', 'scan_point_33_xrd.csv': 'https://data.htmdec.org/#item/69135559e8c9c85bfb382c5e', 'scan_point_34_xrd.csv': 'https://data.htmdec.org/#item/6913555de8c9c85bfb382c82', 'scan_point_35_xrd.csv': 'https://data.htmdec.org/#item/69135560229b1dbc1a73734d', 'scan_point_36_xrd.csv': 'https://data.htmdec.org/#item/6913556478f878bb03651201', 'scan_point_37_xrd.csv': 'https://data.htmdec.org/#item/6913556878f878bb0365121c', 'scan_point_38_xrd.csv': 'https://data.htmdec.org/#item/6913556c78f878bb0365122b', 'scan_point_39_xrd.csv': 'https://data.htmdec.org/#item/691355709ca0e7d06ecd3334', 'scan_point_3_xrd.csv': 'https://data.htmdec.org/#item/6913557378f878bb03651243', 'scan_point_40_xrd.csv': 'https://data.htmdec.org/#item/6913557678f878bb03651252', 'scan_point_41_xrd.csv': 'https://data.htmdec.org/#item/6913557978f878bb03651261', 'scan_point_42_xrd.csv': 'https://data.htmdec.org/#item/6913557d9ca0e7d06ecd3376', 'scan_point_43_xrd.csv': 'https://data.htmdec.org/#item/691355809ca0e7d06ecd338b', 'scan_point_44_xrd.csv': 'https://data.htmdec.org/#item/69135584e8c9c85bfb382d1e', 'scan_point_45_xrd.csv': 'https://data.htmdec.org/#item/6913558778f878bb03651291', 'scan_point_46_xrd.csv': 'https://data.htmdec.org/#item/6913558ae8c9c85bfb382d42', 'scan_point_47_xrd.csv': 'https://data.htmdec.org/#item/6913558d78f878bb036512b5', 'scan_point_48_xrd.csv': 'https://data.htmdec.org/#item/6913559178f878bb036512ca', 'scan_point_4_xrd.csv': 'https://data.htmdec.org/#item/691355999ca0e7d06ecd33bb', 'scan_point_5_xrd.csv': 'https://data.htmdec.org/#item/691355bee8c9c85bfb382e3e', 'scan_point_6_xrd.csv': 'https://data.htmdec.org/#item/691355e7e8c9c85bfb382f61', 'scan_point_7_xrd.csv': 'https://data.htmdec.org/#item/6913560b229b1dbc1a737554', 'scan_point_8_xrd.csv': 'https://data.htmdec.org/#item/69135631e8c9c85bfb383021', 'scan_point_9_xrd.csv': 'https://data.htmdec.org/#item/6913565ae8c9c85bfb383075', 'xrd_calibrant_xrd.csv': 'https://data.htmdec.org/#item/691354e2e8c9c85bfb382a36', 'scan_point_49_xrd.csv': 'https://data.htmdec.org/#item/691355959ca0e7d06ecd33b2', 'scan_point_50_xrd.csv': 'https://data.htmdec.org/#item/6913559ce8c9c85bfb382d78', 'scan_point_51_xrd.csv': 'https://data.htmdec.org/#item/691355a078f878bb03651300', 'scan_point_52_xrd.csv': 'https://data.htmdec.org/#item/691355a39ca0e7d06ecd33df', 'scan_point_53_xrd.csv': 'https://data.htmdec.org/#item/691355a7e8c9c85bfb382d9f', 'scan_point_54_xrd.csv': 'https://data.htmdec.org/#item/691355aa229b1dbc1a73738c', 'scan_point_55_xrd.csv': 'https://data.htmdec.org/#item/691355ad229b1dbc1a737398', 'scan_point_56_xrd.csv': 'https://data.htmdec.org/#item/691355b1229b1dbc1a7373aa', 'scan_point_57_xrd.csv': 'https://data.htmdec.org/#item/691355b4e8c9c85bfb382dcf', 'scan_point_58_xrd.csv': 'https://data.htmdec.org/#item/691355b79ca0e7d06ecd3400', 'scan_point_59_xrd.csv': 'https://data.htmdec.org/#item/691355bae8c9c85bfb382e17', 'scan_point_60_xrd.csv': 'https://data.htmdec.org/#item/691355c2e8c9c85bfb382e7d', 'scan_point_61_xrd.csv': 'https://data.htmdec.org/#item/691355c7e8c9c85bfb382eb6', 'scan_point_62_xrd.csv': 'https://data.htmdec.org/#item/691355cb229b1dbc1a7373b6', 'scan_point_63_xrd.csv': 'https://data.htmdec.org/#item/691355ce229b1dbc1a7373cb', 'scan_point_64_xrd.csv': 'https://data.htmdec.org/#item/691355d29ca0e7d06ecd3409', 'scan_point_65_xrd.csv': 'https://data.htmdec.org/#item/691355d5229b1dbc1a73741f', 'scan_point_66_xrd.csv': 'https://data.htmdec.org/#item/691355d9229b1dbc1a73743d', 'scan_point_67_xrd.csv': 'https://data.htmdec.org/#item/691355dce8c9c85bfb382f19', 'scan_point_68_xrd.csv': 'https://data.htmdec.org/#item/691355e0229b1dbc1a737467', 'scan_point_69_xrd.csv': 'https://data.htmdec.org/#item/691355e3e8c9c85bfb382f3b', 'scan_point_70_xrd.csv': 'https://data.htmdec.org/#item/691355eae8c9c85bfb382f7c', 'scan_point_71_xrd.csv': 'https://data.htmdec.org/#item/691355ede8c9c85bfb382f94', 'scan_point_72_xrd.csv': 'https://data.htmdec.org/#item/691355f1e8c9c85bfb382faf', 'scan_point_73_xrd.csv': 'https://data.htmdec.org/#item/691355f4229b1dbc1a7374ac', 'scan_point_74_xrd.csv': 'https://data.htmdec.org/#item/691355f7229b1dbc1a7374c1', 'scan_point_75_xrd.csv': 'https://data.htmdec.org/#item/691355fa9ca0e7d06ecd3457', 'scan_point_76_xrd.csv': 'https://data.htmdec.org/#item/691355fe9ca0e7d06ecd3472', 'scan_point_77_xrd.csv': 'https://data.htmdec.org/#item/69135601229b1dbc1a737500', 'scan_point_78_xrd.csv': 'https://data.htmdec.org/#item/691356059ca0e7d06ecd348d', 'scan_point_79_xrd.csv': 'https://data.htmdec.org/#item/691356089ca0e7d06ecd349c', 'scan_point_80_xrd.csv': 'https://data.htmdec.org/#item/6913560fe8c9c85bfb382fdf', 'scan_point_81_xrd.csv': 'https://data.htmdec.org/#item/691356129ca0e7d06ecd34cf', 'scan_point_82_xrd.csv': 'https://data.htmdec.org/#item/69135615229b1dbc1a73757e', 'scan_point_83_xrd.csv': 'https://data.htmdec.org/#item/69135619229b1dbc1a7375a2', 'scan_point_84_xrd.csv': 'https://data.htmdec.org/#item/6913561c229b1dbc1a7375c6', 'scan_point_85_xrd.csv': 'https://data.htmdec.org/#item/69135620229b1dbc1a7375ea', 'scan_point_86_xrd.csv': 'https://data.htmdec.org/#item/69135623e8c9c85bfb382ff1', 'scan_point_87_xrd.csv': 'https://data.htmdec.org/#item/69135626229b1dbc1a737617', 'scan_point_88_xrd.csv': 'https://data.htmdec.org/#item/6913562ae8c9c85bfb383012', 'scan_point_89_xrd.csv': 'https://data.htmdec.org/#item/6913562d229b1dbc1a73763b', 'scan_point_90_xrd.csv': 'https://data.htmdec.org/#item/69135635e8c9c85bfb38302a', 'scan_point_91_xrd.csv': 'https://data.htmdec.org/#item/6913563a229b1dbc1a737677', 'scan_point_92_xrd.csv': 'https://data.htmdec.org/#item/6913563e9ca0e7d06ecd350b', 'scan_point_93_xrd.csv': 'https://data.htmdec.org/#item/691356429ca0e7d06ecd3529', 'scan_point_94_xrd.csv': 'https://data.htmdec.org/#item/6913564578f878bb0365133f', 'scan_point_95_xrd.csv': 'https://data.htmdec.org/#item/6913564978f878bb0365135a', 'scan_point_96_xrd.csv': 'https://data.htmdec.org/#item/6913564c78f878bb03651378', 'scan_point_97_xrd.csv': 'https://data.htmdec.org/#item/6913564f78f878bb0365138d', 'scan_point_98_xrd.csv': 'https://data.htmdec.org/#item/6913565278f878bb036513ae', 'scan_point_99_xrd.csv': 'https://data.htmdec.org/#item/69135656e8c9c85bfb383063'}</t>
+  </si>
+  <si>
+    <t>{'scan_point_0_xrd.csv': 'https://data.htmdec.org/#item/68f7cdd35960472ae0ec92fa', 'scan_point_1_xrd.csv': 'https://data.htmdec.org/#item/68f7ce1b18f9fc1d4a340d3c', 'scan_point_2_xrd.csv': 'https://data.htmdec.org/#item/68f7ce1e5960472ae0ec930f', 'scan_point_3_xrd.csv': 'https://data.htmdec.org/#item/68f7ce645960472ae0ec931b', 'scan_point_4_xrd.csv': 'https://data.htmdec.org/#item/68f7ce6818f9fc1d4a340d5d', 'scan_point_5_xrd.csv': 'https://data.htmdec.org/#item/68f7ceb65960472ae0ec932d', 'scan_point_6_xrd.csv': 'https://data.htmdec.org/#item/68f7ceb95960472ae0ec9339', 'scan_point_7_xrd.csv': 'https://data.htmdec.org/#item/68f7cebb68c2cae708b4c4bc', 'scan_point_8_xrd.csv': 'https://data.htmdec.org/#item/68f7cf0818f9fc1d4a340d90', 'scan_point_9_xrd.csv': 'https://data.htmdec.org/#item/68f7cf0b18f9fc1d4a340d93', 'scan_point_10_xrd.csv': 'https://data.htmdec.org/#item/68f7cf56e440f024d10bfd5e', 'scan_point_11_xrd.csv': 'https://data.htmdec.org/#item/68f7cf59e440f024d10bfd67', 'scan_point_12_xrd.csv': 'https://data.htmdec.org/#item/68f7cfa218f9fc1d4a340db4', 'scan_point_13_xrd.csv': 'https://data.htmdec.org/#item/68f7cfa55960472ae0ec934b', 'scan_point_14_xrd.csv': 'https://data.htmdec.org/#item/68f7cfa818f9fc1d4a340dc0', 'scan_point_15_xrd.csv': 'https://data.htmdec.org/#item/68f7cff518f9fc1d4a340dcf', 'scan_point_16_xrd.csv': 'https://data.htmdec.org/#item/68f7cff718f9fc1d4a340dd2', 'scan_point_17_xrd.csv': 'https://data.htmdec.org/#item/68f7d042e440f024d10bfd73', 'scan_point_18_xrd.csv': 'https://data.htmdec.org/#item/68f7d046e440f024d10bfd82', 'scan_point_19_xrd.csv': 'https://data.htmdec.org/#item/68f7d04968c2cae708b4c4e3', 'scan_point_20_xrd.csv': 'https://data.htmdec.org/#item/68f7d09168c2cae708b4c4fb', 'scan_point_21_xrd.csv': 'https://data.htmdec.org/#item/68f7d0935960472ae0ec9360', 'scan_point_22_xrd.csv': 'https://data.htmdec.org/#item/68f7d0e268c2cae708b4c507', 'scan_point_23_xrd.csv': 'https://data.htmdec.org/#item/68f7d0e518f9fc1d4a340df3', 'scan_point_24_xrd.csv': 'https://data.htmdec.org/#item/68f7d12e5960472ae0ec937b'}</t>
+  </si>
+  <si>
+    <t>{}</t>
   </si>
   <si>
     <t>AlMg</t>

--- a/augmented_output.xlsx
+++ b/augmented_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
   <si>
     <t>Timestamp</t>
   </si>
@@ -136,6 +136,9 @@
     <t>JHAMAB00019-13</t>
   </si>
   <si>
+    <t>NONEXISTENT_IGSN</t>
+  </si>
+  <si>
     <t>All data available regarding sample material; processing parameters; and EBSD/XRD data should be parsed and reported here.</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
   </si>
   <si>
     <t>C1--20250605--00087</t>
+  </si>
+  <si>
+    <t>NONEXISTENT_PDV</t>
   </si>
   <si>
     <t xml:space="preserve">PDV data should be post-processed to report velocity-time history, spall strength, and HEL values by using these hyper-parameters and the characterization function from Piyush. </t>
@@ -556,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -683,10 +689,10 @@
         <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J2">
         <v>285</v>
@@ -695,7 +701,7 @@
         <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M2">
         <v>1.55E-06</v>
@@ -713,7 +719,7 @@
         <v>-4.37</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S2">
         <v>13922321626.56921</v>
@@ -746,13 +752,13 @@
         <v>975.4740222024132</v>
       </c>
       <c r="AE2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AG2">
         <v>6.6</v>
       </c>
       <c r="AH2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -775,10 +781,10 @@
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J3">
         <v>285</v>
@@ -787,7 +793,7 @@
         <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M3">
         <v>1.55E-06</v>
@@ -805,7 +811,7 @@
         <v>-4.37</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S3">
         <v>19152542751.35801</v>
@@ -838,42 +844,125 @@
         <v>905.7013045502234</v>
       </c>
       <c r="AE3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AG3">
         <v>6.6</v>
       </c>
       <c r="AH3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" t="s">
-        <v>34</v>
+      <c r="A4" s="2">
+        <v>45876.76800179398</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
       </c>
       <c r="F4" t="s">
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4">
+        <v>285</v>
+      </c>
+      <c r="K4">
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="M4">
+        <v>1.55E-06</v>
+      </c>
+      <c r="N4">
+        <v>10</v>
+      </c>
+      <c r="O4">
+        <v>1.550016E-06</v>
+      </c>
+      <c r="P4">
+        <v>7.5</v>
+      </c>
+      <c r="Q4">
+        <v>-4.37</v>
+      </c>
+      <c r="U4">
+        <v>4</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="X4">
+        <v>21.87</v>
+      </c>
+      <c r="Y4">
+        <v>-6.15</v>
+      </c>
+      <c r="Z4">
+        <v>21.3513</v>
+      </c>
+      <c r="AA4">
+        <v>-6.1875</v>
+      </c>
+      <c r="AB4">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AC4">
+        <v>750.59</v>
       </c>
       <c r="AE4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG4">
+        <v>6.6</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>49</v>
+      </c>
+      <c r="U5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC5" t="s">
         <v>53</v>
       </c>
-      <c r="AG4" t="s">
-        <v>54</v>
+      <c r="AE5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
